--- a/Procurement/_документы/План закупок ЦАКФ – IV кв. 2026.xlsx
+++ b/Procurement/_документы/План закупок ЦАКФ – IV кв. 2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="294">
   <si>
     <t>Утвержден Решением Управляющего Совета</t>
   </si>
@@ -109,36 +109,15 @@
     <t>Комплект на рабочее место: монитор 24" IPS Full HD, проводная клавиатура и мышь, гарнитура с микрофоном.</t>
   </si>
   <si>
-    <t>Мебель: рабочее место (стол, кресло, тумба)</t>
-  </si>
-  <si>
-    <t>Стол, эргономичное кресло, тумба. 16 рабочих мест в open space и 3 гостевых (продакшн-группа, региональные координаторы в приезд).</t>
-  </si>
-  <si>
-    <t>Мебель кабинетов руководства</t>
-  </si>
-  <si>
     <t>Оснащение</t>
   </si>
   <si>
-    <t>Мебель переговорной</t>
-  </si>
-  <si>
-    <t>Стол переговорный и 12 стульев.</t>
-  </si>
-  <si>
     <t>ноябрь 2026</t>
   </si>
   <si>
-    <t>Шкафы для документов и сейф</t>
-  </si>
-  <si>
     <t>МФУ цветное А3</t>
   </si>
   <si>
-    <t>Тонеры CMYK для МФУ А3</t>
-  </si>
-  <si>
     <t>Стартовый и резервный комплекты по 4 цвета, оригинальные или рекомендованные производителем.</t>
   </si>
   <si>
@@ -154,72 +133,9 @@
     <t>ноябрь–декабрь 2026</t>
   </si>
   <si>
-    <t>Конференц-камера и спикерфон</t>
-  </si>
-  <si>
-    <t>Комплект для ВКС с акиматами и региональными координаторами: камера с широким углом, спикерфон.</t>
-  </si>
-  <si>
     <t>Товар, работа</t>
   </si>
   <si>
-    <t>Сетевое оборудование и СКС с монтажом</t>
-  </si>
-  <si>
-    <t>Сетевой накопитель (NAS) с дисками</t>
-  </si>
-  <si>
-    <t>Кинокамера Canon EOS C70</t>
-  </si>
-  <si>
-    <t>Кинокамера Canon EOS C70 Cinema Camera (арт. 5659): сенсор Super 35 DGO, крепление RF, встроенные ND-фильтры, запись 4K. Гарантия производителя, доставка.</t>
-  </si>
-  <si>
-    <t>Объектив Canon RF 24-105mm f/4L IS USM</t>
-  </si>
-  <si>
-    <t>Штатный зум-объектив с байонетом RF (арт. 2584), стабилизация, для съёмки мероприятий.</t>
-  </si>
-  <si>
-    <t>Электронный стабилизатор DJI RS 4 Pro Combo</t>
-  </si>
-  <si>
-    <t>Трёхосевой стабилизатор для камеры с нагрузкой до 4,5 кг (арт. 6218), в комплектации Combo.</t>
-  </si>
-  <si>
-    <t>Монопод E-Image MA600+610FH</t>
-  </si>
-  <si>
-    <t>Монопод с видеоголовой (арт. 3288) для съёмки мероприятий.</t>
-  </si>
-  <si>
-    <t>Видеоштатив с видеоголовой</t>
-  </si>
-  <si>
-    <t>Штатив для видеосъёмки с жидкостной видеоголовой, нагрузка не менее 8 кг, чехол.</t>
-  </si>
-  <si>
-    <t>Сумка для видеокамеры E-Image OSCAR S50</t>
-  </si>
-  <si>
-    <t>Транспортная сумка для кинокамеры и оптики (арт. 1756, EB0925).</t>
-  </si>
-  <si>
-    <t>Беспроводная микрофонная система DJI Mic 3</t>
-  </si>
-  <si>
-    <t>Карта памяти Sony 128GB SF-G Tough UHS-II SDXC</t>
-  </si>
-  <si>
-    <t>Внешний SSD 2 ТБ</t>
-  </si>
-  <si>
-    <t>Внешний твердотельный накопитель для исходных материалов, интерфейс USB 3.2 / USB-C.</t>
-  </si>
-  <si>
-    <t>Аккумулятор Canon BP-A30</t>
-  </si>
-  <si>
     <t>Бытовая техника (комплект: кулер, холодильник, микроволновая печь, кофемашина)</t>
   </si>
   <si>
@@ -271,45 +187,6 @@
     <t>Техническое обслуживание МФУ А3 и А4, поставка расходных материалов.</t>
   </si>
   <si>
-    <t>Бумага для печати А4, 80 г/м²</t>
-  </si>
-  <si>
-    <t>Бумага для печати А3, 80 г/м²</t>
-  </si>
-  <si>
-    <t>Блок бумаги для флипчарта</t>
-  </si>
-  <si>
-    <t>Плотная бумага и обложки для брошюровки</t>
-  </si>
-  <si>
-    <t>Ручки, карандаши, маркеры, текстовыделители</t>
-  </si>
-  <si>
-    <t>Блокноты, стикеры, закладки</t>
-  </si>
-  <si>
-    <t>Папки-регистраторы, скоросшиватели, файлы А4</t>
-  </si>
-  <si>
-    <t>Конверты, почтовые пакеты, бумага для заметок</t>
-  </si>
-  <si>
-    <t>Скобы, скрепки, клей, ножницы, ножи, линейки</t>
-  </si>
-  <si>
-    <t>Степлеры, дыроколы, лотки, органайзеры</t>
-  </si>
-  <si>
-    <t>Архивные короба и файлы для архива</t>
-  </si>
-  <si>
-    <t>Короба, папки и файлы для архивного хранения документов проекта, нить и шило для подшивки.</t>
-  </si>
-  <si>
-    <t>Батарейки, удлинители, мелкая электрика</t>
-  </si>
-  <si>
     <t>Товар, услуга</t>
   </si>
   <si>
@@ -322,9 +199,6 @@
     <t>Canva Teams / Adobe Creative Cloud</t>
   </si>
   <si>
-    <t>Zoom Pro</t>
-  </si>
-  <si>
     <t>Продвижение в социальных сетях (таргетированная реклама)</t>
   </si>
   <si>
@@ -346,12 +220,6 @@
     <t>Медиа</t>
   </si>
   <si>
-    <t>Прочие</t>
-  </si>
-  <si>
-    <t>Страхование оборудования</t>
-  </si>
-  <si>
     <t>Страхование работников от несчастных случаев (ОСНС)</t>
   </si>
   <si>
@@ -520,48 +388,9 @@
     <t>b2bcompany.kz/catalog/khozyaystvennye_tovary/bytovaya_khimiya/universalnoe_moyushchee_sredstvo/</t>
   </si>
   <si>
-    <t>Оснащение; однородные ТРУ «мебель» ниже 8 000 МРП</t>
-  </si>
-  <si>
-    <t>Стеллажи металлические для склада и архива</t>
-  </si>
-  <si>
     <t>Сборка, доставка и подъём мебели и стеллажей</t>
   </si>
   <si>
-    <t>Ламинатор Deli ET104, А3</t>
-  </si>
-  <si>
-    <t>Ламинатор пакетный А3, 300 мм/мин.</t>
-  </si>
-  <si>
-    <t>Оснащение; цена b2bcompany.kz на 24.09.2026</t>
-  </si>
-  <si>
-    <t>Плёнка для ламинирования А4, 100 мкм</t>
-  </si>
-  <si>
-    <t>Упаковка 100 шт. (OfficeSpace или аналог).</t>
-  </si>
-  <si>
-    <t>Переплётная машина Deli 3873</t>
-  </si>
-  <si>
-    <t>Для пластиковой пружины: перфорирует до 18 листов, сшивает до 425 листов.</t>
-  </si>
-  <si>
-    <t>Расходные материалы для переплёта</t>
-  </si>
-  <si>
-    <t>Оснащение; цены b2bcompany.kz на 24.09.2026</t>
-  </si>
-  <si>
-    <t>Оснащение; цена Kaspi.kz на 30.09.2026</t>
-  </si>
-  <si>
-    <t>Электронный архив документов, фото- и видеоматериалов проекта, RAID, диски в комплекте.</t>
-  </si>
-  <si>
     <t>Сетевые фильтры на рабочие места</t>
   </si>
   <si>
@@ -598,66 +427,24 @@
     <t>Копирайтинг (аутсорс)</t>
   </si>
   <si>
-    <t>Дизайн (аутсорс)</t>
-  </si>
-  <si>
     <t>Работа с креаторами и креативными проектами (аутсорс)</t>
   </si>
   <si>
-    <t>Прочие; без НДС</t>
-  </si>
-  <si>
     <t>Командировки; НДС в тарифе. Суточные и местный транспорт возмещаются по авансовому отчёту</t>
   </si>
   <si>
-    <t>Протокол № 13 от «___» октября 2026 года</t>
-  </si>
-  <si>
-    <t>2. Аутсорс-услуги (юрист МФЦА, сис.админ, разработчик, режиссёр, копирайтер, дизайнер, менеджер по креаторам)</t>
-  </si>
-  <si>
     <t>Core i7 / Ryzen 7 и выше, 32 ГБ ОЗУ, SSD 1 ТБ, дискретная графика – руководитель департамента цифрового развития, фотограф-рилсмейкер (монтаж).</t>
   </si>
   <si>
-    <t>Стойка ресепшн</t>
-  </si>
-  <si>
-    <t>Стойка ресепшн.</t>
-  </si>
-  <si>
-    <t>Шкафы для документов (делопроизводство, кадры, договоры) и офисный сейф для документов и печатей.</t>
-  </si>
-  <si>
-    <t>Стеллажи 2000×1000×500 мм, 4–5 полок: склад фото- и видеотехники, архив документов.</t>
-  </si>
-  <si>
-    <t>Доставка, подъём на этаж и сборка рабочих мест, мебели кабинетов, переговорной, стойки ресепшн, шкафов, сейфа и стеллажей.</t>
-  </si>
-  <si>
     <t>Класс Kyocera TASKalfa 2554ci: печать, копирование и сканирование А3 в цвете, дуплекс, автоподатчик, сетевой и Wi-Fi модуль, тумба, доставка и установка.</t>
   </si>
   <si>
     <t>Класс HP LaserJet Pro MFP 4103fdw / Kyocera ECOSYS MA4000fx: Wi-Fi, дуплекс, автоподатчик; печать, копирование, сканирование. Размещение – ресепшн и кабинет аппарата.</t>
   </si>
   <si>
-    <t>Интерактивная панель 75"</t>
-  </si>
-  <si>
-    <t>Для зала совещаний: 4K, сенсорная, Android (класс Iiyama ProLite TE7515A-B2AG) – совещания, презентации, ВКС, работа со схемами.</t>
-  </si>
-  <si>
     <t>Оснащение; цена Kaspi.kz на 10.10.2026</t>
   </si>
   <si>
-    <t>Мобильная стойка для панели на колёсах</t>
-  </si>
-  <si>
-    <t>Стойка для панели 32–75″ (AVA-1500 или аналог) – у стола совещаний.</t>
-  </si>
-  <si>
-    <t>Маршрутизатор, коммутатор, точки доступа Wi-Fi, кабельная система, монтаж и настройка в помещениях 701–702 и зоне 710 (7 этаж).</t>
-  </si>
-  <si>
     <t>5 розеток, 3 м, с заземлением (Defender ES или аналог) – по одному на рабочее место новых сотрудников и 2 у стола совещаний.</t>
   </si>
   <si>
@@ -670,36 +457,6 @@
     <t>Линейно-интерактивный, 1200 ВА / 650 Вт (APC Back-UPS BX1200MI-GR или аналог) – рабочие места и сетевое оборудование.</t>
   </si>
   <si>
-    <t>Оснащение – фото-видео, лот 1; КП PSP Digital от 12.09.2026</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 1; КП PSP Digital</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 2; КП PSP Digital</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 2; оценка</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 3; КП PSP Digital</t>
-  </si>
-  <si>
-    <t>Скорость до 299 Мбайт/с (арт. 4240).</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 4; КП PSP Digital</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 4; оценка</t>
-  </si>
-  <si>
-    <t>Запасной аккумулятор для кинокамеры Canon EOS C70.</t>
-  </si>
-  <si>
-    <t>Оснащение – фото-видео, лот 5; оценка</t>
-  </si>
-  <si>
     <t>Комплект на кухонную зону: кулер для воды, холодильник, микроволновая печь, кофемашина.</t>
   </si>
   <si>
@@ -724,36 +481,6 @@
     <t>Офис; текущий поставщик – ТОО «Пони Экспресс»</t>
   </si>
   <si>
-    <t>Пачка 500 листов, класс C и выше (SvetoCopy Classic или аналог) – 3,5 пачки в месяц.</t>
-  </si>
-  <si>
-    <t>Офис – канцелярия, лот 1; цена b2bcompany.kz</t>
-  </si>
-  <si>
-    <t>Офис – канцелярия, лот 1</t>
-  </si>
-  <si>
-    <t>Комплект письменных принадлежностей – 10 комплектов в месяц.</t>
-  </si>
-  <si>
-    <t>Офис – канцелярия, лот 2; цена b2bcompany.kz</t>
-  </si>
-  <si>
-    <t>Блокнот, стикеры, клейкие закладки – 10 комплектов в месяц.</t>
-  </si>
-  <si>
-    <t>Разово при открытии офиса: папки-регистраторы, скоросшиватели, файлы-вкладыши, разделители – договоры, кадры, переписка.</t>
-  </si>
-  <si>
-    <t>Разово при открытии офиса.</t>
-  </si>
-  <si>
-    <t>Разово при открытии офиса: степлеры, дыроколы, лотки для бумаг, настольные органайзеры.</t>
-  </si>
-  <si>
-    <t>Разово при открытии офиса: батарейки АА, ААА и CR2032, мелкая электрика – техника, пульты, микрофоны.</t>
-  </si>
-  <si>
     <t>Представительские расходы: кофе-брейки на рабочих встречах</t>
   </si>
   <si>
@@ -763,78 +490,27 @@
     <t>Корпоративная почта, Teams, OneDrive, офисные приложения – 14 пользователей (новые сотрудники 2026 года).</t>
   </si>
   <si>
-    <t>Съёмка и монтаж видео, ролики – с 01.11.2026, 2 месяца по 1 160 000 ₸.</t>
-  </si>
-  <si>
-    <t>Тексты для соцсетей, сайта, СМИ – с 01.11.2026, 2 месяца по 812 000 ₸.</t>
-  </si>
-  <si>
-    <t>Визуалы, инфографика, макеты – с 01.11.2026, 2 месяца по 812 000 ₸.</t>
-  </si>
-  <si>
-    <t>Работа с креаторами, креативные проекты – с 01.11.2026, 2 месяца по 812 000 ₸.</t>
-  </si>
-  <si>
-    <t>Медиа; 150 000 ₸ в месяц без НДС. Текущий поставщик – ТОО «Albatech Print»</t>
-  </si>
-  <si>
-    <t>Нотариальные услуги</t>
-  </si>
-  <si>
-    <t>Доверенности, засвидетельствование копий – разово.</t>
-  </si>
-  <si>
-    <t>Страхование фото- и видеооборудования – 1/4 годовой суммы 100 000 ₸.</t>
-  </si>
-  <si>
-    <t>Годовой полис обязательного страхования работников от несчастных случаев на 14 новых сотрудников 2026 года (оценка: тариф 0,29% от годового ФОТ).</t>
-  </si>
-  <si>
     <t>ОСНС; без НДС</t>
   </si>
   <si>
     <t>Услуга, работа</t>
   </si>
   <si>
-    <t>Услуги, работы по реализации проектов</t>
-  </si>
-  <si>
-    <t>Первоочередные проекты проектного офиса «Таза Қазақстан».</t>
-  </si>
-  <si>
     <t>Открытый конкурс / ЗЦП (по лотам)</t>
   </si>
   <si>
     <t>Проекты</t>
   </si>
   <si>
-    <t>Авиабилеты и бронирование гостиниц: 14,3 поездки по РК (билет 90 000 ₸ + 2 ночи × 30 000 ₸); зарубежных командировок в 2026 году нет.</t>
-  </si>
-  <si>
-    <t>1. Персонал: оклады и отчисления работодателя</t>
-  </si>
-  <si>
     <t>3. ОСНС: годовой полис на новых сотрудников</t>
   </si>
   <si>
-    <t>4. Командировки по РК (в плане – авиабилеты и гостиницы)</t>
-  </si>
-  <si>
-    <t>5. Оснащение (разово)</t>
-  </si>
-  <si>
-    <t>6. Офис: аренда, депозит, хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские</t>
-  </si>
-  <si>
     <t>7. Цифровые инструменты</t>
   </si>
   <si>
     <t>8. Медиа: таргет, полиграфия, подписки</t>
   </si>
   <si>
-    <t>Непредвиденные расходы: резерв 10% и прочие (нотариус, страхование оборудования)</t>
-  </si>
-  <si>
     <t>Б. Первоочередные проекты</t>
   </si>
   <si>
@@ -844,57 +520,24 @@
     <t>Финансовый год: 2026 год (IV квартал – октябрь–декабрь)</t>
   </si>
   <si>
-    <t>Комплект на кабинет: рабочий стол, кресло, шкаф, стол для совещаний – ГИД, два заместителя, национальный координатор, финансовый директор.</t>
-  </si>
-  <si>
     <t>Ресурс около 3 000 страниц, по 2 картриджа на аппарат – запас на первый год.</t>
   </si>
   <si>
-    <t>Обложки А4 картонные и пластиковые, пружины 6, 10, 14 и 51 мм – по 100 шт.</t>
-  </si>
-  <si>
     <t>3 розетки, с заземлением, ПВС 3×1 мм², 16 А – от колонн к островным блокам столов.</t>
   </si>
   <si>
     <t>Секция 2 м – прокладка удлинителей через проходы.</t>
   </si>
   <si>
-    <t>Комплект на двух говорящих (арт. 6976): два передатчика, приёмник, кейс для зарядки – интервью и синхронная запись.</t>
-  </si>
-  <si>
-    <t>Мелкий ремонт, сантехника, электрика, мебельная фурнитура – по заявкам.</t>
-  </si>
-  <si>
-    <t>Пачка 500 листов, класс C и выше – схемы, плакаты, раздаточные материалы.</t>
-  </si>
-  <si>
-    <t>Блок 20 листов, 60×90 или 64×96 см, 80 г/м² – совещания и семинары.</t>
-  </si>
-  <si>
-    <t>Плотная бумага 200–300 г/м², картонные и пластиковые обложки, пружины – отчёты и методические материалы.</t>
-  </si>
-  <si>
-    <t>Конверты С5, В4, Е4+, почтовые пакеты, блоки для заметок – переписка с МЭПР и акиматами.</t>
-  </si>
-  <si>
     <t>Дашборды мониторинга акции – 3 пользователя.</t>
   </si>
   <si>
     <t>Дизайн визуалов, инфографики и презентаций – 2 лицензии.</t>
   </si>
   <si>
-    <t>ИТ-инфраструктура, сеть и техника; делопроизводство, хозяйственное администрирование, ассистирование – с 21.10.2026, 2,35 месяца по 812 000 ₸.</t>
-  </si>
-  <si>
-    <t>Разработка и сопровождение ИИ- и ГИС-инструментов, цифровой платформы – с 21.10.2026, 2,35 месяца по 1 160 000 ₸.</t>
-  </si>
-  <si>
     <t>Цены текущего поставщика канцелярских и хозяйственных товаров – ТОО «Acvee Market Astana» (b2bcompany.kz)</t>
   </si>
   <si>
-    <t>Проверено на сайте 17.09.2026. Договор B2B22/07082025 (папка поставщика в D:\Закупки\2 Поставщики). Поставщик – на общеустановленном режиме и плательщик НДС (письмо № 10 от 20.10.2025); цены сайта совпадают с ценами счёта № AM-5960 от 08.05.2026, то есть НДС в них включён. При объёмной закупке запросить прайс со скидкой и счёт на оплату.</t>
-  </si>
-  <si>
     <t>Блок бумаги для флипчарта "Kuvert", 60×90 см, 20 л, 80 гр/м² – от; "Berlingo", 64×96 см, 20 л – 4 090 ₸</t>
   </si>
   <si>
@@ -913,25 +556,358 @@
     <t>Универсальное моющее средство "Yarko", 5 л – 3 395 ₸; "Mr.Proper", Лимон, 5 л – 8 335 ₸</t>
   </si>
   <si>
+    <t>План закупок товаров, работ и неконсультационных услуг ЦАКФ на IV квартал 2026 года</t>
+  </si>
+  <si>
+    <t>Администрирование (аутсорс)</t>
+  </si>
+  <si>
+    <t>Стол рабочий с подкатной тумбой, 140×70 см</t>
+  </si>
+  <si>
+    <t>Столешница ЛДСП, каркас металл, размеры 140×70×77,7 см; в комплекте подкатная тумба на колёсах с тремя ящиками и фронтальная панель. Класс ZETA Лофт или эквивалент не хуже по каждому параметру. Доставка, занос и сборка в офисе Заказчика.</t>
+  </si>
+  <si>
+    <t>Кресло рабочее офисное</t>
+  </si>
+  <si>
+    <t>Крестовина с колёсами, спинка из сетки, подлокотники, регулировка высоты сиденья 450–550 мм, наклон спинки до 95°, обивка гобелен, нагрузка не менее 120 кг. Класс МИ-6 Z или эквивалент.</t>
+  </si>
+  <si>
+    <t>Кресло руководителя</t>
+  </si>
+  <si>
+    <t>Высокая спинка, механизм качания, подлокотники, крестовина с колёсами, регулировка высоты, обивка гобелен, нагрузка не менее 120 кг. Класс ZETA Гермес или эквивалент. Кабинеты заместителя ГИД, финансового директора, национального координатора и советника.</t>
+  </si>
+  <si>
+    <t>Кресло Главного исполнительного директора</t>
+  </si>
+  <si>
+    <t>Высокая спинка, обивка экокожа, крестовина с колёсами, регулировка высоты, нагрузка не менее 120 кг. Класс ZETA мод. 2338 или эквивалент.</t>
+  </si>
+  <si>
+    <t>Стул офисный для посетителей</t>
+  </si>
+  <si>
+    <t>Каркас металл, обивка рогожка или гобелен, скруглённая спинка, нагрузка не менее 100 кг, высота сиденья 45–50 см, штабелируемый. Класс ZETA СМ 6 или эквивалент.</t>
+  </si>
+  <si>
+    <t>Стул представительский</t>
+  </si>
+  <si>
+    <t>Каркас металл, обивка велюр, мягкие сиденье и спинка, размеры около 87×55×57 см. Класс ZETA Shugyla или эквивалент. Кабинет ГИД и приёмная.</t>
+  </si>
+  <si>
+    <t>Шкаф для документов закрытый, с замком</t>
+  </si>
+  <si>
+    <t>Полностью закрытый шкаф для документов: 1–2 двери с замком, 4 полки, габариты около 42,5×37×176 см, металл или ЛДСП. Класс ZETA ШММ-1 или эквивалент. Кабинет финансового директора.</t>
+  </si>
+  <si>
+    <t>Комплект мебели кабинета руководителя, 6 предметов</t>
+  </si>
+  <si>
+    <t>Стол овальный 180×80 см, приставка 140×65 см, тумба 120×40 см, шкаф и стеллаж 210×180 см; ЛДСП, тон венге тёмный. Класс ILMER Рук или эквивалент. Кабинеты ГИД и руководителя проектного офиса.</t>
+  </si>
+  <si>
+    <t>Комплект мебели кабинета руководителя, 5 предметов</t>
+  </si>
+  <si>
+    <t>Шкаф плательный 800×400×1950 мм с полкой для головных уборов и турникетом, шкаф для документов 800×400×1950 мм, стол письменный 1100×600×750 мм, стол с выдвижной полкой для клавиатуры 800×600×750 мм, приставка угловая 600×600 мм; ЛДСП и ДВП, тон венге тёмный. Класс АТЛАНТИК К103 или эквивалент, тон коричневый. Кабинеты заместителя ГИД и финансового директора.</t>
+  </si>
+  <si>
+    <t>Кухонный гарнитур, 200 см</t>
+  </si>
+  <si>
+    <t>Верхние и нижние шкафы, столешница ЛДСП; габариты 200×215×60 см. Класс ZETA Денвер или эквивалент. Мойка и смеситель – отдельной позицией.</t>
+  </si>
+  <si>
+    <t>Мойка врезная со смесителем</t>
+  </si>
+  <si>
+    <t>Мойка врезная 60×45×22 см, нержавеющая сталь 3 мм; в комплекте смеситель, сифон, перелив, дозатор, коландер, сетка и решётка для сушки.</t>
+  </si>
+  <si>
+    <t>Врезка мойки, подключение воды и канализации</t>
+  </si>
+  <si>
+    <t>Врезка мойки в столешницу кухонного гарнитура, подключение смесителя к водоснабжению и канализации на кухонной зоне.</t>
+  </si>
+  <si>
+    <t>Доставка, подъём на 7 этаж и сборка рабочих мест, комплектов мебели кабинетов руководства, кухонного гарнитура, шкафов и стульев.</t>
+  </si>
+  <si>
+    <t>Стартовый комплект тонеров CMYK для МФУ А3</t>
+  </si>
+  <si>
+    <t>Резервный комплект тонеров CMYK для МФУ А3</t>
+  </si>
+  <si>
+    <t>Второй комплект тонеров вслед за стартовым.</t>
+  </si>
+  <si>
+    <t>Мобильная стойка на колёсах под телевизор 40″</t>
+  </si>
+  <si>
+    <t>Стойка напольная на колёсах, сталь, высота 120–150 см, диагональ 32–65″, нагрузка не менее 45 кг. Класс Onkron TS1351 или эквивалент.</t>
+  </si>
+  <si>
+    <t>Оснащение; цена Kaspi.kz на 23.10.2026</t>
+  </si>
+  <si>
+    <t>Мобильная стойка на колёсах под тяжёлый телевизор</t>
+  </si>
+  <si>
+    <t>Стойка напольная на колёсах под имеющийся тяжёлый телевизор: нагрузка не менее 100 кг, диагональ 55–86″, VESA до 800×600. Класс SK-200 или эквивалент.</t>
+  </si>
+  <si>
+    <t>Конференц-камера и спикерфон с установкой</t>
+  </si>
+  <si>
+    <t>Конференц-камера с широким углом обзора и спикерфон для зала совещаний: подключение по USB, совместимость с Zoom и Teams; в стоимость входят установка и настройка.</t>
+  </si>
+  <si>
+    <t>Wi-Fi роутер 5G с SIM-картой</t>
+  </si>
+  <si>
+    <t>Роутер 5G со слотом для SIM-карты и Wi-Fi, поддержка сетей 5G, 4G и 3G. Класс ALTEL 5G H155-380 или эквивалент. Второй роутер к уже имеющемуся.</t>
+  </si>
+  <si>
+    <t>Оснащение; цена Kaspi.kz на 27.10.2026</t>
+  </si>
+  <si>
+    <t>Внешний SSD 2 ТБ для исходников</t>
+  </si>
+  <si>
+    <t>Внешний твердотельный накопитель 2 ТБ, USB 3.2, для хранения исходных фото- и видеоматериалов.</t>
+  </si>
+  <si>
+    <t>Жалюзи вертикальные тканевые</t>
+  </si>
+  <si>
+    <t>Вертикальные тканевые жалюзи на окна зоны 710 с замером, изготовлением и установкой. В кабинетах 701–702 жалюзи уже есть, их монтаж учтён в позиции текущего мелкого ремонта.</t>
+  </si>
+  <si>
+    <t>Декоративное растение напольное в кашпо</t>
+  </si>
+  <si>
+    <t>Декоративное дерево в высоком напольном кашпо для зоны ресепшн и переговорной.</t>
+  </si>
+  <si>
+    <t>Оснащение; цена Kaspi.kz на 19.10.2026</t>
+  </si>
+  <si>
+    <t>Вешалка-стойка напольная</t>
+  </si>
+  <si>
+    <t>Вешалка-стойка на крестовине, стойка с семью крючками, металл, габариты около 50×50×175 см. Класс ZETA Кактус или эквивалент. Приёмная, переговорная, open space.</t>
+  </si>
+  <si>
+    <t>Оснащение; цена Kaspi.kz на 24.10.2026</t>
+  </si>
+  <si>
+    <t>Гарантийный депозит по аренде офиса</t>
+  </si>
+  <si>
+    <t>Гарантийный депозит в размере одной месячной ставки аренды, возвращается по окончании договора аренды. БЦ «Сыганак», ул. Сыганак, 70, 7 этаж.</t>
+  </si>
+  <si>
+    <t>Офис; возвратный платёж по договору аренды</t>
+  </si>
+  <si>
+    <t>Мелкий ремонт, сантехника, электрика, мебельная фурнитура по заявкам; монтаж уже имеющихся жалюзи в кабинетах 701–702.</t>
+  </si>
+  <si>
+    <t>Мобильный интернет для двух Wi-Fi роутеров, безлимит</t>
+  </si>
+  <si>
+    <t>Безлимитный мобильный интернет на максимальной скорости в сетях 5G, 4G и 3G, по одному номеру на роутер, два роутера. Класс тарифа ALTEL «Шаңырақ» или эквивалент.</t>
+  </si>
+  <si>
+    <t>Офис; цена altel.kz на 27.10.2026</t>
+  </si>
+  <si>
+    <t>Канцелярия и бумага – ежемесячная потребность</t>
+  </si>
+  <si>
+    <t>Бумага А4 и А3, бумага для флипчарта, ручки, карандаши, маркеры, текстовыделители, блокноты, стикеры, закладки – на месяц работы офиса. Состав и объёмы – лист «Канцелярия» бюджета.</t>
+  </si>
+  <si>
+    <t>Офис; цены b2bcompany.kz на 24.09.2026</t>
+  </si>
+  <si>
+    <t>Канцелярские принадлежности при открытии офиса</t>
+  </si>
+  <si>
+    <t>Папки-регистраторы, скоросшиватели, файлы А4, батарейки, удлинители и мелкая электрика, датер автоматический со штемпельной краской – разово при открытии офиса. Состав – лист «Канцелярия» бюджета.</t>
+  </si>
+  <si>
+    <t>Zoom, тариф «Профессиональный» – годовая подписка</t>
+  </si>
+  <si>
+    <t>Годовая подписка на одну лицензию: видео-конференц-связь с регионами, до 100 участников, запись в облако.</t>
+  </si>
+  <si>
+    <t>ноябрь 2026 – ноябрь 2027</t>
+  </si>
+  <si>
+    <t>Битрикс24, тариф «Стандартный» (до 50 пользователей)</t>
+  </si>
+  <si>
+    <t>Облачная подписка: CRM, задачи и проекты, диск, чат, до 50 пользователей. Оплата помесячно за всю организацию, не за пользователя.</t>
+  </si>
+  <si>
+    <t>Цифровые; цена bitrix24.kz на 24.10.2026</t>
+  </si>
+  <si>
+    <t>Медиа; текущий поставщик – ТОО «Albatech Print»</t>
+  </si>
+  <si>
+    <t>Нотариальные расходы и пострегистрационные услуги МФЦА</t>
+  </si>
+  <si>
+    <t>Нотариальные услуги (доверенности, засвидетельствование копий) и две пострегистрационные услуги МФЦА по регистрации изменений в учредительные документы.</t>
+  </si>
+  <si>
+    <t>Договоры и соглашения, право МФЦА, сопровождение сделок – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>ИТ-инфраструктура, сеть и техника, делопроизводство, хозяйственное администрирование, ассистирование – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Разработка и сопровождение ИИ- и ГИС-инструментов, цифровой платформы – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Съёмка и монтаж видео, ролики для соцсетей и мероприятий – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Тексты для соцсетей, сайта и СМИ – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Социологические услуги (аутсорс)</t>
+  </si>
+  <si>
+    <t>Опросы и полевые работы, обработка и анализ данных – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Работа с креаторами и креативными проектами – 2 месяца. В цену входят оплата труда специалиста с налогами работодателя, вознаграждение аутстаффера 10% и НДС.</t>
+  </si>
+  <si>
+    <t>Годовой полис обязательного страхования работников от несчастных случаев на новых сотрудников 2026 года.</t>
+  </si>
+  <si>
+    <t>Проект «TAZA TALQY»: встречи в регионах</t>
+  </si>
+  <si>
+    <t>Проведение встреч с жителями и молодёжью в 6 регионах: проезд и проживание организаторов и спикеров, фото- и видеосъёмка, продвижение в соцсетях, амбассадор-модератор.</t>
+  </si>
+  <si>
+    <t>Презентация и запуск деятельности проектного офиса</t>
+  </si>
+  <si>
+    <t>Организация и проведение презентации проектного офиса «Таза Қазақстан».</t>
+  </si>
+  <si>
+    <t>Специальные и креативные проекты</t>
+  </si>
+  <si>
+    <t>Реализация специальных и креативных проектов проектного офиса.</t>
+  </si>
+  <si>
+    <t>Информационное сопровождение проектов и деятельности</t>
+  </si>
+  <si>
+    <t>Информационное сопровождение проектов и деятельности проектного офиса.</t>
+  </si>
+  <si>
+    <t>Социологическое исследование</t>
+  </si>
+  <si>
+    <t>Проведение социологического исследования по тематике проекта.</t>
+  </si>
+  <si>
+    <t>Первый этап разработки цифровой платформы</t>
+  </si>
+  <si>
+    <t>Первый этап разработки цифровой платформы проекта.</t>
+  </si>
+  <si>
+    <t>Авиабилеты и бронирование гостиниц по РК: 19,9 поездки (билет 90 000 ₸ туда-обратно + 2 ночи × 30 000 ₸); зарубежных командировок в 2026 году нет.</t>
+  </si>
+  <si>
+    <t>1а. Премия 8 работникам проектного офиса по итогам работы в октябре (выплата в декабре)</t>
+  </si>
+  <si>
+    <t>2. Аутсорс-услуги: юрист МФЦА, администратор, разработчик, режиссёр, копирайтер, социолог, менеджер по креаторам (с вознаграждением аутстаффера 10% и НДС)</t>
+  </si>
+  <si>
+    <t>4. Командировки по РК (в плане – только авиабилеты и гостиницы)</t>
+  </si>
+  <si>
+    <t>5. Оснащение (разово): техника, мебель, МФУ, электрика, кухня</t>
+  </si>
+  <si>
+    <t>Офис; без НДС</t>
+  </si>
+  <si>
+    <t>Протокол № 12 от 30 октября 2026 года</t>
+  </si>
+  <si>
     <t>План закупок ЦАКФ на IV квартал 2026 года – сверка с бюджетом (бюджет – без НДС, аутсорс – с НДС; план закупок – с НДС 16%)</t>
   </si>
   <si>
-    <t>Проект от 14.10.2026. Бюджет – «Бюджет ЦАКФ на октябрь–декабрь 2026 года», лист «Свод». Детализация плана – лист «IV кв. 2026».</t>
-  </si>
-  <si>
-    <t>План закупок товаров, работ и неконсультационных услуг ЦАКФ на IV квартал 2026 года</t>
-  </si>
-  <si>
-    <t>Проект от 14.10.2026. Составлен по бюджету «Бюджет ЦАКФ на октябрь–декабрь 2026 года». Цены и суммы – с НДС 16%; страхование – без НДС; в авиабилетах НДС включён в тариф. Способы закупок – по Правилам закупок Фонда: ЗЦП (п. 37, до 8 000 МРП), электронный магазин (гл. 8), из одного источника (п. 46), открытый конкурс (гл. 5).</t>
-  </si>
-  <si>
-    <t>Видео-конференц-связь с регионами – лицензия.</t>
-  </si>
-  <si>
-    <t>Договоры и соглашения, право МФЦА – с 21.10.2026, 2,35 месяца по 1 160 000 ₸.</t>
-  </si>
-  <si>
-    <t>Администрирование (аутсорс)</t>
+    <t>1. Персонал: оклады, отчисления работодателя, обязательства по оплате труда за июль–октябрь</t>
+  </si>
+  <si>
+    <t>6. Офис: аренда, депозит, хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские, нотариус и услуги МФЦА, прочие обязательства</t>
+  </si>
+  <si>
+    <t>Резерв 10% на непредвиденные расходы</t>
+  </si>
+  <si>
+    <t>НДС: 16% на закупки, аренду, услуги, подписки и первоочередные проекты; расчёты с бюджетом по НДС (в плане – в суммах позиций)</t>
+  </si>
+  <si>
+    <t>Сверка бюджета и плана закупок</t>
+  </si>
+  <si>
+    <t>Бюджет на IV квартал 2026 года, всего</t>
+  </si>
+  <si>
+    <t>План закупок с НДС</t>
+  </si>
+  <si>
+    <t>Не входит в план закупок:</t>
+  </si>
+  <si>
+    <t>оплата труда, отчисления, премия, обязательства по оплате труда</t>
+  </si>
+  <si>
+    <t>резерв 10% и НДС на него</t>
+  </si>
+  <si>
+    <t>суточные и местный транспорт в командировках</t>
+  </si>
+  <si>
+    <t>обязательства по НДС за прошлые периоды</t>
+  </si>
+  <si>
+    <t>прочие обязательства</t>
+  </si>
+  <si>
+    <t>Округление цен по строкам плана</t>
+  </si>
+  <si>
+    <t>Разница бюджета и плана с учетом позиций вне плана</t>
+  </si>
+  <si>
+    <t>Составлен по бюджету Фонда на IV квартал 2026 года (252,4 млн тенге). Состав лотов, количество закупаемых товаров, работ и услуг могут изменяться в пределах утвержденной суммы плана закупок. Цены и суммы – с НДС 16%; страхование, гарантийный депозит и нотариальные услуги – без НДС; в авиабилетах НДС включён в тариф. Способы закупок – по Правилам закупок Фонда: ЗЦП (п. 37, до 8 000 МРП), электронный магазин (гл. 8), из одного источника (п. 46), открытый конкурс (гл. 5).</t>
+  </si>
+  <si>
+    <t>Бюджет Фонда на IV квартал 2026 года, лист «Свод», столбцы «Октябрь-ноябрь 2026» и «Декабрь 2026». Детализация плана – лист «IV кв. 2026».</t>
+  </si>
+  <si>
+    <t>Договор B2B22/07082025. Поставщик – на общеустановленном режиме и плательщик НДС (письмо № 10 от 20.10.2025); цены сайта совпадают с ценами счёта № AM-5960 от 08.05.2026, то есть НДС в них включён.</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1082,6 +1058,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -1372,7 +1355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.7109375" customWidth="1"/>
@@ -1383,34 +1366,34 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B5" s="16">
-        <v>58691748</v>
+        <v>84494370</v>
       </c>
       <c r="C5" s="16">
         <v>0</v>
@@ -1421,29 +1404,28 @@
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>195</v>
+        <v>269</v>
       </c>
       <c r="B6" s="16">
-        <v>14567355</v>
+        <v>9389520</v>
       </c>
       <c r="C6" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Аутсорс*",'IV кв. 2026'!I11:I90)</f>
-        <v>14567355</v>
+        <v>0</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="15"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B7" s="16">
-        <v>500000</v>
+        <v>13763192</v>
       </c>
       <c r="C7" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"ОСНС*",'IV кв. 2026'!I11:I90)</f>
-        <v>500000</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Аутсорс*",'IV кв. 2026'!I11:I83)</f>
+        <v>13763192</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
@@ -1451,29 +1433,29 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>263</v>
+        <v>158</v>
       </c>
       <c r="B8" s="16">
-        <v>3783804</v>
+        <v>645095</v>
       </c>
       <c r="C8" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Командировки*",'IV кв. 2026'!I11:I90)</f>
-        <v>2141129</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"ОСНС*",'IV кв. 2026'!I11:I83)</f>
+        <v>645095</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
       <c r="F8" s="15"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B9" s="16">
-        <v>29170035</v>
+        <v>3799012</v>
       </c>
       <c r="C9" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Оснащение*",'IV кв. 2026'!I11:I90)</f>
-        <v>33262540</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Командировки*",'IV кв. 2026'!I11:I83)</f>
+        <v>2984362</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
@@ -1481,29 +1463,29 @@
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B10" s="16">
-        <v>17530038</v>
+        <v>14032043</v>
       </c>
       <c r="C10" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Офис*",'IV кв. 2026'!I11:I90)</f>
-        <v>14607523</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Оснащение*",'IV кв. 2026'!I11:I83)</f>
+        <v>16277182</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="15"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B11" s="16">
-        <v>589500</v>
+        <v>17874450</v>
       </c>
       <c r="C11" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Цифровые*",'IV кв. 2026'!I11:I90)</f>
-        <v>683820</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Офис*",'IV кв. 2026'!I11:I83)</f>
+        <v>19340177</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="16"/>
@@ -1511,29 +1493,29 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>267</v>
+        <v>159</v>
       </c>
       <c r="B12" s="16">
-        <v>2525000</v>
+        <v>586447</v>
       </c>
       <c r="C12" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Медиа*",'IV кв. 2026'!I11:I90)</f>
-        <v>2929000</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Цифровые*",'IV кв. 2026'!I11:I83)</f>
+        <v>680278</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
       <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>268</v>
+        <v>160</v>
       </c>
       <c r="B13" s="16">
-        <v>12810748</v>
+        <v>2350000</v>
       </c>
       <c r="C13" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Прочие*",'IV кв. 2026'!I11:I90)</f>
-        <v>83000</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Медиа*",'IV кв. 2026'!I11:I83)</f>
+        <v>2726000</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="16"/>
@@ -1541,63 +1523,76 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B14" s="16">
-        <v>87404855</v>
+        <v>11648913</v>
       </c>
       <c r="C14" s="16">
-        <f>SUMIF('IV кв. 2026'!M11:M90,"Проекты*",'IV кв. 2026'!I11:I90)</f>
-        <v>87404855</v>
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Прочие*",'IV кв. 2026'!I11:I83)</f>
+        <v>0</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
       <c r="F14" s="15"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="14">
-        <f>SUM(B5:B14)</f>
-        <v>227573083</v>
-      </c>
-      <c r="C15" s="14">
-        <f>SUM(C5:C14)</f>
-        <v>156179222</v>
+      <c r="A15" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="16">
+        <v>70077146</v>
+      </c>
+      <c r="C15" s="16">
+        <f>SUMIF('IV кв. 2026'!M11:M83,"Проекты*",'IV кв. 2026'!I11:I83)</f>
+        <v>81289489</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="16"/>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" s="16"/>
+        <v>279</v>
+      </c>
+      <c r="B16" s="16">
+        <v>23696298</v>
+      </c>
       <c r="C16" s="16">
-        <f>'IV кв. 2026'!I91</f>
-        <v>156179222</v>
+        <v>0</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
       <c r="F16" s="15"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="A17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="14">
+        <f>SUM(B5:B16)</f>
+        <v>252356486</v>
+      </c>
+      <c r="C17" s="14">
+        <f>SUM(C5:C16)</f>
+        <v>137705775</v>
+      </c>
       <c r="D17" s="16"/>
       <c r="E17" s="16"/>
       <c r="F17" s="15"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="A18" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16">
+        <f>'IV кв. 2026'!I84</f>
+        <v>137705775</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="15"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
@@ -1608,7 +1603,9 @@
       <c r="F19" s="17"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
+      <c r="A20" s="20" t="s">
+        <v>280</v>
+      </c>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1616,80 +1613,124 @@
       <c r="F20" s="17"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
+      <c r="A21" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="19">
+        <f>B17</f>
+        <v>252356486</v>
+      </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
+      <c r="A22" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B22" s="19">
+        <f>C17</f>
+        <v>137705775</v>
+      </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="17"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
+      <c r="A23" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" s="19"/>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
+    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24" s="19">
+        <f>B5+B6</f>
+        <v>93883890</v>
+      </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" s="19">
+        <v>12115182</v>
+      </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
       <c r="F25" s="17"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
+      <c r="A26" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B26" s="19">
+        <f>B9-C9</f>
+        <v>814650</v>
+      </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
       <c r="F26" s="17"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
+      <c r="A27" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B27" s="19">
+        <v>7355000</v>
+      </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
+      <c r="A28" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="B28" s="19">
+        <v>482000</v>
+      </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
       <c r="F28" s="17"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
+      <c r="A29" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="19">
+        <f>B21-B22-SUM(B24:B28)</f>
+        <v>-11</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="19">
+        <f>B21-B22-SUM(B24:B29)</f>
+        <v>0</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -1934,6 +1975,14 @@
       <c r="D60" s="17"/>
       <c r="E60" s="17"/>
       <c r="F60" s="17"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
+      <c r="D61" s="17"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1946,7 +1995,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2008,28 +2057,28 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>194</v>
+        <v>274</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
+      <c r="A4" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
@@ -2049,25 +2098,25 @@
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2083,21 +2132,21 @@
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
+      <c r="A8" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
     </row>
     <row r="9" spans="1:13" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
@@ -2201,14 +2250,14 @@
         <v>20</v>
       </c>
       <c r="G11" s="6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H11" s="6">
         <v>522000</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" ref="I11:I42" si="0">ROUND(G11*H11,0)</f>
-        <v>6264000</v>
+        <v>2088000</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>21</v>
@@ -2220,7 +2269,7 @@
         <v>23</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -2237,20 +2286,20 @@
         <v>24</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="6">
         <v>1044000</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="0"/>
-        <v>2088000</v>
+        <v>1044000</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>21</v>
@@ -2262,7 +2311,7 @@
         <v>23</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -2285,14 +2334,14 @@
         <v>20</v>
       </c>
       <c r="G13" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H13" s="6">
         <v>116000</v>
       </c>
       <c r="I13" s="6">
         <f t="shared" si="0"/>
-        <v>1160000</v>
+        <v>580000</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>21</v>
@@ -2304,10 +2353,10 @@
         <v>23</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>1</v>
       </c>
@@ -2318,23 +2367,23 @@
         <v>17</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="6">
-        <v>232000</v>
+        <v>80861</v>
       </c>
       <c r="I14" s="6">
         <f t="shared" si="0"/>
-        <v>4408000</v>
+        <v>1617220</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>21</v>
@@ -2346,10 +2395,10 @@
         <v>23</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>1</v>
       </c>
@@ -2360,23 +2409,23 @@
         <v>17</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>29</v>
+        <v>180</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>272</v>
+        <v>181</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="6">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H15" s="6">
-        <v>580000</v>
+        <v>17110</v>
       </c>
       <c r="I15" s="6">
         <f t="shared" si="0"/>
-        <v>2900000</v>
+        <v>444860</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>21</v>
@@ -2388,10 +2437,10 @@
         <v>23</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1</v>
       </c>
@@ -2402,23 +2451,23 @@
         <v>17</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>31</v>
+        <v>182</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="6">
-        <v>928000</v>
+        <v>70900</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="0"/>
-        <v>928000</v>
+        <v>283600</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>21</v>
@@ -2430,12 +2479,12 @@
         <v>23</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="8">
         <v>7</v>
@@ -2444,10 +2493,10 @@
         <v>17</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>20</v>
@@ -2456,26 +2505,26 @@
         <v>1</v>
       </c>
       <c r="H17" s="6">
-        <v>290000</v>
+        <v>114460</v>
       </c>
       <c r="I17" s="6">
         <f t="shared" si="0"/>
-        <v>290000</v>
+        <v>114460</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>1</v>
       </c>
@@ -2486,40 +2535,40 @@
         <v>17</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H18" s="6">
-        <v>522000</v>
+        <v>7595</v>
       </c>
       <c r="I18" s="6">
         <f t="shared" si="0"/>
-        <v>522000</v>
+        <v>151900</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="8">
         <v>9</v>
@@ -2528,38 +2577,38 @@
         <v>17</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="6">
-        <v>69600</v>
+        <v>26905</v>
       </c>
       <c r="I19" s="6">
         <f t="shared" si="0"/>
-        <v>139200</v>
+        <v>80715</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1</v>
       </c>
@@ -2567,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>20</v>
@@ -2582,11 +2631,11 @@
         <v>1</v>
       </c>
       <c r="H20" s="6">
-        <v>918720</v>
+        <v>45900</v>
       </c>
       <c r="I20" s="6">
         <f t="shared" si="0"/>
-        <v>918720</v>
+        <v>45900</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>21</v>
@@ -2598,10 +2647,10 @@
         <v>23</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>1</v>
       </c>
@@ -2612,38 +2661,38 @@
         <v>17</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="6">
-        <v>2900000</v>
+        <v>249999</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="0"/>
-        <v>2900000</v>
+        <v>499998</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>1</v>
       </c>
@@ -2654,10 +2703,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>36</v>
+        <v>194</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>20</v>
@@ -2666,26 +2715,26 @@
         <v>2</v>
       </c>
       <c r="H22" s="6">
-        <v>348000</v>
+        <v>265000</v>
       </c>
       <c r="I22" s="6">
         <f t="shared" si="0"/>
-        <v>696000</v>
+        <v>530000</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>1</v>
       </c>
@@ -2696,40 +2745,40 @@
         <v>17</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6">
-        <v>324800</v>
+        <v>118860</v>
       </c>
       <c r="I23" s="6">
         <f t="shared" si="0"/>
-        <v>649600</v>
+        <v>118860</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="8">
         <v>14</v>
@@ -2738,38 +2787,38 @@
         <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>39</v>
+        <v>198</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>273</v>
+        <v>199</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G24" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6">
-        <v>63800</v>
+        <v>36990</v>
       </c>
       <c r="I24" s="6">
         <f t="shared" si="0"/>
-        <v>255200</v>
+        <v>36990</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <v>2</v>
       </c>
@@ -2777,85 +2826,85 @@
         <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G25" s="6">
         <v>1</v>
       </c>
       <c r="H25" s="6">
-        <v>42340</v>
+        <v>25000</v>
       </c>
       <c r="I25" s="6">
         <f t="shared" si="0"/>
-        <v>42340</v>
+        <v>25000</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" s="8">
         <v>16</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G26" s="6">
         <v>1</v>
       </c>
       <c r="H26" s="6">
-        <v>6000</v>
+        <v>381736</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>381736</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B27" s="8">
         <v>17</v>
@@ -2864,40 +2913,40 @@
         <v>17</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>172</v>
+        <v>29</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G27" s="6">
         <v>1</v>
       </c>
       <c r="H27" s="6">
-        <v>114327</v>
+        <v>2900000</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="0"/>
-        <v>114327</v>
+        <v>2900000</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" s="8">
         <v>18</v>
@@ -2906,40 +2955,40 @@
         <v>17</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>274</v>
+        <v>30</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G28" s="6">
         <v>1</v>
       </c>
       <c r="H28" s="6">
-        <v>48700</v>
+        <v>348000</v>
       </c>
       <c r="I28" s="6">
         <f t="shared" si="0"/>
-        <v>48700</v>
+        <v>348000</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" s="8">
         <v>19</v>
@@ -2948,35 +2997,35 @@
         <v>17</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>204</v>
+        <v>31</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="6">
-        <v>989997</v>
+        <v>324800</v>
       </c>
       <c r="I29" s="6">
         <f t="shared" si="0"/>
-        <v>989997</v>
+        <v>649600</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>206</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -2990,40 +3039,40 @@
         <v>17</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G30" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" s="6">
-        <v>49990</v>
+        <v>63800</v>
       </c>
       <c r="I30" s="6">
         <f t="shared" si="0"/>
-        <v>49990</v>
+        <v>255200</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>206</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" s="8">
         <v>21</v>
@@ -3032,13 +3081,13 @@
         <v>17</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>42</v>
+        <v>204</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G31" s="6">
         <v>1</v>
@@ -3054,43 +3103,43 @@
         <v>21</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="8">
         <v>22</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G32" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H32" s="6">
-        <v>928000</v>
+        <v>4118</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="0"/>
-        <v>928000</v>
+        <v>86478</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>21</v>
@@ -3102,7 +3151,7 @@
         <v>23</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3116,38 +3165,38 @@
         <v>17</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G33" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6">
-        <v>812000</v>
+        <v>6101</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="0"/>
-        <v>812000</v>
+        <v>18303</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>2</v>
       </c>
@@ -3158,23 +3207,23 @@
         <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G34" s="6">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H34" s="6">
-        <v>4118</v>
+        <v>7235</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="0"/>
-        <v>65888</v>
+        <v>28940</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>21</v>
@@ -3186,7 +3235,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3200,23 +3249,23 @@
         <v>17</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>180</v>
+        <v>125</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G35" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H35" s="6">
-        <v>6101</v>
+        <v>9039</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="0"/>
-        <v>18303</v>
+        <v>90390</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>21</v>
@@ -3228,12 +3277,12 @@
         <v>23</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" s="8">
         <v>26</v>
@@ -3242,23 +3291,23 @@
         <v>17</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>275</v>
+        <v>142</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G36" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H36" s="6">
-        <v>7235</v>
+        <v>89302</v>
       </c>
       <c r="I36" s="6">
         <f t="shared" si="0"/>
-        <v>28940</v>
+        <v>893020</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>21</v>
@@ -3270,10 +3319,10 @@
         <v>23</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
         <v>2</v>
       </c>
@@ -3284,40 +3333,40 @@
         <v>17</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G37" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6">
-        <v>9039</v>
+        <v>56990</v>
       </c>
       <c r="I37" s="6">
         <f t="shared" si="0"/>
-        <v>45195</v>
+        <v>56990</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="5" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" s="8">
         <v>28</v>
@@ -3326,52 +3375,52 @@
         <v>17</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G38" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6">
-        <v>89302</v>
+        <v>111605</v>
       </c>
       <c r="I38" s="6">
         <f t="shared" si="0"/>
-        <v>893020</v>
+        <v>111605</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" s="8">
         <v>29</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>20</v>
@@ -3380,26 +3429,26 @@
         <v>1</v>
       </c>
       <c r="H39" s="6">
-        <v>1669990</v>
+        <v>348000</v>
       </c>
       <c r="I39" s="6">
         <f t="shared" si="0"/>
-        <v>1669990</v>
+        <v>348000</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
         <v>1</v>
       </c>
@@ -3410,29 +3459,29 @@
         <v>17</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>50</v>
+        <v>214</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G40" s="6">
         <v>1</v>
       </c>
       <c r="H40" s="6">
-        <v>485990</v>
+        <v>36238</v>
       </c>
       <c r="I40" s="6">
         <f t="shared" si="0"/>
-        <v>485990</v>
+        <v>36238</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>23</v>
@@ -3452,40 +3501,40 @@
         <v>17</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>51</v>
+        <v>216</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>52</v>
+        <v>217</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6">
-        <v>479990</v>
+        <v>174000</v>
       </c>
       <c r="I41" s="6">
         <f t="shared" si="0"/>
-        <v>479990</v>
+        <v>348000</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" s="8">
         <v>32</v>
@@ -3494,40 +3543,40 @@
         <v>17</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G42" s="6">
         <v>1</v>
       </c>
       <c r="H42" s="6">
-        <v>58990</v>
+        <v>464000</v>
       </c>
       <c r="I42" s="6">
         <f t="shared" si="0"/>
-        <v>58990</v>
+        <v>464000</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>216</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" s="8">
         <v>33</v>
@@ -3536,38 +3585,38 @@
         <v>17</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G43" s="6">
         <v>1</v>
       </c>
       <c r="H43" s="6">
-        <v>250000</v>
+        <v>35990</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" ref="I43:I74" si="1">ROUND(G43*H43,0)</f>
-        <v>250000</v>
+        <v>35990</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L43" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>2</v>
       </c>
@@ -3575,13 +3624,13 @@
         <v>34</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>20</v>
@@ -3590,26 +3639,26 @@
         <v>1</v>
       </c>
       <c r="H44" s="6">
-        <v>31990</v>
+        <v>428736</v>
       </c>
       <c r="I44" s="6">
         <f t="shared" si="1"/>
-        <v>31990</v>
+        <v>428736</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>1</v>
       </c>
@@ -3620,35 +3669,35 @@
         <v>17</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>277</v>
+        <v>221</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G45" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6">
-        <v>119990</v>
+        <v>30701</v>
       </c>
       <c r="I45" s="6">
         <f t="shared" si="1"/>
-        <v>119990</v>
+        <v>92103</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -3659,55 +3708,55 @@
         <v>36</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>219</v>
+        <v>39</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G46" s="6">
         <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>104990</v>
+        <v>174000</v>
       </c>
       <c r="I46" s="6">
         <f t="shared" si="1"/>
-        <v>104990</v>
+        <v>174000</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>220</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" s="8">
         <v>37</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>20</v>
@@ -3716,26 +3765,26 @@
         <v>1</v>
       </c>
       <c r="H47" s="6">
-        <v>150000</v>
+        <v>464000</v>
       </c>
       <c r="I47" s="6">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>464000</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>1</v>
       </c>
@@ -3746,10 +3795,10 @@
         <v>17</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>20</v>
@@ -3758,28 +3807,28 @@
         <v>1</v>
       </c>
       <c r="H48" s="6">
-        <v>240000</v>
+        <v>11600</v>
       </c>
       <c r="I48" s="6">
         <f t="shared" si="1"/>
-        <v>240000</v>
+        <v>11600</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>223</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" s="8">
         <v>39</v>
@@ -3788,52 +3837,52 @@
         <v>17</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>224</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G49" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H49" s="6">
-        <v>464000</v>
+        <v>8950</v>
       </c>
       <c r="I49" s="6">
         <f t="shared" si="1"/>
-        <v>464000</v>
+        <v>44750</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" s="8">
         <v>40</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>226</v>
+        <v>149</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>40</v>
@@ -3842,26 +3891,26 @@
         <v>1</v>
       </c>
       <c r="H50" s="6">
-        <v>35990</v>
+        <v>13300639</v>
       </c>
       <c r="I50" s="6">
         <f t="shared" si="1"/>
-        <v>35990</v>
+        <v>13300639</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>1</v>
       </c>
@@ -3869,41 +3918,41 @@
         <v>41</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G51" s="6">
         <v>1</v>
       </c>
       <c r="H51" s="6">
-        <v>174000</v>
+        <v>4869152</v>
       </c>
       <c r="I51" s="6">
         <f t="shared" si="1"/>
-        <v>174000</v>
+        <v>4869152</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>2</v>
       </c>
@@ -3911,55 +3960,55 @@
         <v>42</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>71</v>
+        <v>229</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G52" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="6">
-        <v>464000</v>
+        <v>116000</v>
       </c>
       <c r="I52" s="6">
         <f t="shared" si="1"/>
-        <v>464000</v>
+        <v>232000</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" s="8">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>227</v>
+        <v>47</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>228</v>
+        <v>48</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>20</v>
@@ -3968,26 +4017,26 @@
         <v>2</v>
       </c>
       <c r="H53" s="6">
-        <v>11600</v>
+        <v>34800</v>
       </c>
       <c r="I53" s="6">
         <f t="shared" si="1"/>
-        <v>23200</v>
+        <v>69600</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>1</v>
       </c>
@@ -3995,80 +4044,80 @@
         <v>44</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>229</v>
+        <v>49</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="G54" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="6">
-        <v>13409903</v>
+        <v>58000</v>
       </c>
       <c r="I54" s="6">
         <f t="shared" si="1"/>
-        <v>13409903</v>
+        <v>116000</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="8">
         <v>45</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>73</v>
+        <v>230</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G55" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="6">
-        <v>58000</v>
+        <v>5490</v>
       </c>
       <c r="I55" s="6">
         <f t="shared" si="1"/>
-        <v>174000</v>
+        <v>21960</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M55" s="5" t="s">
-        <v>74</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4079,41 +4128,41 @@
         <v>46</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G56" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="6">
-        <v>69600</v>
+        <v>34800</v>
       </c>
       <c r="I56" s="6">
         <f t="shared" si="1"/>
-        <v>208800</v>
+        <v>69600</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>1</v>
       </c>
@@ -4121,125 +4170,125 @@
         <v>47</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="G57" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6">
-        <v>58000</v>
+        <v>27985</v>
       </c>
       <c r="I57" s="6">
         <f t="shared" si="1"/>
-        <v>174000</v>
+        <v>55970</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B58" s="8">
         <v>48</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G58" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H58" s="6">
-        <v>34800</v>
+        <v>23256</v>
       </c>
       <c r="I58" s="6">
         <f t="shared" si="1"/>
-        <v>104400</v>
+        <v>23256</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>74</v>
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" s="8">
         <v>49</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G59" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H59" s="6">
-        <v>2450</v>
+        <v>116000</v>
       </c>
       <c r="I59" s="6">
         <f t="shared" si="1"/>
-        <v>26950</v>
+        <v>232000</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>1</v>
       </c>
@@ -4247,38 +4296,38 @@
         <v>50</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>279</v>
+        <v>153</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G60" s="6">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="H60" s="6">
-        <v>5990</v>
+        <v>8120</v>
       </c>
       <c r="I60" s="6">
         <f t="shared" si="1"/>
-        <v>5990</v>
+        <v>308560</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>233</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4289,38 +4338,38 @@
         <v>51</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="F61" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G61" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H61" s="6">
-        <v>4090</v>
+        <v>8700</v>
       </c>
       <c r="I61" s="6">
         <f t="shared" si="1"/>
-        <v>8180</v>
+        <v>52200</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>233</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4331,251 +4380,251 @@
         <v>52</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>281</v>
+        <v>168</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G62" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6">
-        <v>5800</v>
+        <v>34800</v>
       </c>
       <c r="I62" s="6">
         <f t="shared" si="1"/>
-        <v>5800</v>
+        <v>139200</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B63" s="8">
         <v>53</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>85</v>
+        <v>238</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F63" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G63" s="6">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H63" s="6">
-        <v>1200</v>
+        <v>92158</v>
       </c>
       <c r="I63" s="6">
         <f t="shared" si="1"/>
-        <v>36000</v>
+        <v>92158</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" s="8">
         <v>54</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G64" s="6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H64" s="6">
-        <v>900</v>
+        <v>44080</v>
       </c>
       <c r="I64" s="6">
         <f t="shared" si="1"/>
-        <v>27000</v>
+        <v>88160</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B65" s="8">
         <v>55</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G65" s="6">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6">
-        <v>1500</v>
+        <v>2320000</v>
       </c>
       <c r="I65" s="6">
         <f t="shared" si="1"/>
-        <v>22500</v>
+        <v>2320000</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>236</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" s="8">
         <v>56</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>282</v>
+        <v>60</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G66" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6">
-        <v>8000</v>
+        <v>174000</v>
       </c>
       <c r="I66" s="6">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>348000</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B67" s="8">
         <v>57</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>239</v>
+        <v>62</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G67" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6">
-        <v>10000</v>
+        <v>29000</v>
       </c>
       <c r="I67" s="6">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>58000</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>2</v>
       </c>
@@ -4583,41 +4632,41 @@
         <v>58</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>90</v>
+        <v>245</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G68" s="6">
         <v>1</v>
       </c>
       <c r="H68" s="6">
-        <v>6000</v>
+        <v>350000</v>
       </c>
       <c r="I68" s="6">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>350000</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>1</v>
       </c>
@@ -4625,125 +4674,125 @@
         <v>59</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G69" s="6">
         <v>2</v>
       </c>
       <c r="H69" s="6">
-        <v>12000</v>
+        <v>1106930</v>
       </c>
       <c r="I69" s="6">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>2213860</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B70" s="8">
         <v>60</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G70" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="6">
-        <v>8000</v>
+        <v>543066</v>
       </c>
       <c r="I70" s="6">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>1086132</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K70" s="5" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M70" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" s="8">
         <v>61</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>242</v>
+        <v>130</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G71" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" s="6">
-        <v>116000</v>
+        <v>1276000</v>
       </c>
       <c r="I71" s="6">
         <f t="shared" si="1"/>
-        <v>348000</v>
+        <v>2552000</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M71" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>1</v>
       </c>
@@ -4751,41 +4800,41 @@
         <v>62</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G72" s="6">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="H72" s="6">
-        <v>8120</v>
+        <v>1276000</v>
       </c>
       <c r="I72" s="6">
         <f t="shared" si="1"/>
-        <v>341040</v>
+        <v>2552000</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>2</v>
       </c>
@@ -4793,41 +4842,41 @@
         <v>63</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G73" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H73" s="6">
-        <v>8700</v>
+        <v>893200</v>
       </c>
       <c r="I73" s="6">
         <f t="shared" si="1"/>
-        <v>78300</v>
+        <v>1786400</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>2</v>
       </c>
@@ -4835,41 +4884,41 @@
         <v>64</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>97</v>
+        <v>252</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>284</v>
+        <v>253</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G74" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H74" s="6">
-        <v>34800</v>
+        <v>893200</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="1"/>
-        <v>208800</v>
+        <v>1786400</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>2</v>
       </c>
@@ -4877,38 +4926,38 @@
         <v>65</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G75" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H75" s="6">
-        <v>9280</v>
+        <v>893200</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" ref="I75:I90" si="2">ROUND(G75*H75,0)</f>
-        <v>55680</v>
+        <f t="shared" ref="I75:I83" si="2">ROUND(G75*H75,0)</f>
+        <v>1786400</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M75" s="5" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -4919,13 +4968,13 @@
         <v>66</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>185</v>
+        <v>64</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>20</v>
@@ -4934,26 +4983,26 @@
         <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>2731613</v>
+        <v>645095</v>
       </c>
       <c r="I76" s="6">
         <f t="shared" si="2"/>
-        <v>2731613</v>
+        <v>645095</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M76" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>1</v>
       </c>
@@ -4961,38 +5010,38 @@
         <v>67</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>301</v>
+        <v>256</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G77" s="6">
         <v>1</v>
       </c>
       <c r="H77" s="6">
-        <v>1912129</v>
+        <v>8317601</v>
       </c>
       <c r="I77" s="6">
         <f t="shared" si="2"/>
-        <v>1912129</v>
+        <v>8317601</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -5003,41 +5052,41 @@
         <v>68</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>187</v>
+        <v>258</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G78" s="6">
         <v>1</v>
       </c>
       <c r="H78" s="6">
-        <v>2731613</v>
+        <v>7441168</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="2"/>
-        <v>2731613</v>
+        <v>7441168</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="8">
         <v>1</v>
       </c>
@@ -5045,521 +5094,227 @@
         <v>69</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G79" s="6">
         <v>1</v>
       </c>
       <c r="H79" s="6">
-        <v>2320000</v>
+        <v>13366293</v>
       </c>
       <c r="I79" s="6">
         <f t="shared" si="2"/>
-        <v>2320000</v>
+        <v>13366293</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" s="8">
         <v>70</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G80" s="6">
         <v>1</v>
       </c>
       <c r="H80" s="6">
-        <v>1624000</v>
+        <v>18120747</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="2"/>
-        <v>1624000</v>
+        <v>18120747</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B81" s="8">
         <v>71</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>190</v>
+        <v>264</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G81" s="6">
         <v>1</v>
       </c>
       <c r="H81" s="6">
-        <v>1624000</v>
+        <v>15205280</v>
       </c>
       <c r="I81" s="6">
         <f t="shared" si="2"/>
-        <v>1624000</v>
+        <v>15205280</v>
       </c>
       <c r="J81" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B82" s="8">
         <v>72</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>191</v>
+        <v>266</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="G82" s="6">
         <v>1</v>
       </c>
       <c r="H82" s="6">
-        <v>1624000</v>
+        <v>18838400</v>
       </c>
       <c r="I82" s="6">
         <f t="shared" si="2"/>
-        <v>1624000</v>
+        <v>18838400</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>23</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B83" s="8">
         <v>73</v>
       </c>
       <c r="C83" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D83" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="E83" s="5" t="s">
-        <v>100</v>
+        <v>268</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G83" s="6">
         <v>1</v>
       </c>
       <c r="H83" s="6">
-        <v>2320000</v>
+        <v>2984362</v>
       </c>
       <c r="I83" s="6">
         <f t="shared" si="2"/>
-        <v>2320000</v>
+        <v>2984362</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>21</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
-        <v>2</v>
-      </c>
-      <c r="B84" s="8">
-        <v>74</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="6">
-        <v>1</v>
-      </c>
-      <c r="H84" s="6">
-        <v>522000</v>
-      </c>
-      <c r="I84" s="6">
-        <f t="shared" si="2"/>
-        <v>522000</v>
-      </c>
-      <c r="J84" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K84" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L84" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M84" s="5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
-        <v>3</v>
-      </c>
-      <c r="B85" s="8">
-        <v>75</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F85" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G85" s="6">
-        <v>3</v>
-      </c>
-      <c r="H85" s="6">
-        <v>29000</v>
-      </c>
-      <c r="I85" s="6">
-        <f t="shared" si="2"/>
-        <v>87000</v>
-      </c>
-      <c r="J85" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L85" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M85" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="8">
-        <v>2</v>
-      </c>
-      <c r="B86" s="8">
-        <v>76</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" s="6">
-        <v>1</v>
-      </c>
-      <c r="H86" s="6">
-        <v>58000</v>
-      </c>
-      <c r="I86" s="6">
-        <f t="shared" si="2"/>
-        <v>58000</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L86" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M86" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="8">
-        <v>2</v>
-      </c>
-      <c r="B87" s="8">
-        <v>77</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="F87" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G87" s="6">
-        <v>1</v>
-      </c>
-      <c r="H87" s="6">
-        <v>25000</v>
-      </c>
-      <c r="I87" s="6">
-        <f t="shared" si="2"/>
-        <v>25000</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L87" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M87" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A88" s="8">
-        <v>1</v>
-      </c>
-      <c r="B88" s="8">
-        <v>78</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" s="6">
-        <v>1</v>
-      </c>
-      <c r="H88" s="6">
-        <v>500000</v>
-      </c>
-      <c r="I88" s="6">
-        <f t="shared" si="2"/>
-        <v>500000</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L88" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M88" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="8">
-        <v>1</v>
-      </c>
-      <c r="B89" s="8">
-        <v>79</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="G89" s="6">
-        <v>1</v>
-      </c>
-      <c r="H89" s="6">
-        <v>87404855</v>
-      </c>
-      <c r="I89" s="6">
-        <f t="shared" si="2"/>
-        <v>87404855</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L89" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M89" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A90" s="8">
-        <v>1</v>
-      </c>
-      <c r="B90" s="8">
-        <v>80</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G90" s="6">
-        <v>1</v>
-      </c>
-      <c r="H90" s="6">
-        <v>2141129</v>
-      </c>
-      <c r="I90" s="6">
-        <f t="shared" si="2"/>
-        <v>2141129</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L90" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="M90" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E91" s="4"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="7"/>
-      <c r="I91" s="7">
-        <f>SUM(I11:I90)</f>
-        <v>156179222</v>
-      </c>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7">
+        <f>SUM(I11:I83)</f>
+        <v>137705775</v>
+      </c>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5586,267 +5341,267 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="C5" s="12">
         <v>2450</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="C6" s="12">
         <v>2150</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="C7" s="12">
         <v>5990</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>289</v>
+        <v>170</v>
       </c>
       <c r="C8" s="12">
         <v>2155</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="C9" s="12">
         <v>35</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="C10" s="12">
         <v>190</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="C11" s="12">
         <v>1019</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C12" s="12">
         <v>14</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="C13" s="12">
         <v>680</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>292</v>
+        <v>173</v>
       </c>
       <c r="C14" s="12">
         <v>165</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="C15" s="12">
         <v>560</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="C16" s="12">
         <v>661</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>293</v>
+        <v>174</v>
       </c>
       <c r="C17" s="12">
         <v>285</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="C18" s="12">
         <v>3395</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
